--- a/AAII_Financials/Quarterly/DVCMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DVCMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="92">
   <si>
     <t>DVCMY</t>
   </si>
@@ -656,77 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +774,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +821,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +868,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +891,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +934,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +981,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1028,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1075,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1095,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1138,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1185,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1208,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1251,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1298,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1345,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1392,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1439,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1486,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1533,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1580,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1627,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1674,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1721,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1768,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1815,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1862,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1909,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +1956,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2031,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,377 +2050,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>797400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>804800</v>
+      </c>
+      <c r="F41" s="3">
         <v>825800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>559400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
         <v>689800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>595100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>685600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>680900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>465300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>680900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>465300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>426900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F42" s="3">
         <v>12600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>7400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>7400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>15400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>15300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>15100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>15300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>15100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>576500</v>
+      </c>
+      <c r="F43" s="3">
         <v>469500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>566100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>534600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>634100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>527500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>566400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>397500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>566400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>397500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>364700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2027900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2046600</v>
+      </c>
+      <c r="F44" s="3">
         <v>2020800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2000600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
         <v>1763200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1918900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1384400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1363000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1081200</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>1363000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1081200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>992100</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>63400</v>
+      </c>
+      <c r="F45" s="3">
         <v>117600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>63700</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>16300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>22100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>42900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>24900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>12200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>24900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>12200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3521100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3553600</v>
+      </c>
+      <c r="F46" s="3">
         <v>3479500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3251400</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
         <v>3041900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3226200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2670400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2682100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1980800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>2682100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1980800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1817400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>66900</v>
+      </c>
+      <c r="F47" s="3">
         <v>67700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>135800</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
         <v>107800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>62300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>59200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>67200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>63700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>67200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>63700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1778800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1795200</v>
+      </c>
+      <c r="F48" s="3">
         <v>1809600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1702800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
         <v>1571500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1386800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1163600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1004500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>926800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>1004500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>926800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3978100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4014800</v>
+      </c>
+      <c r="F49" s="3">
         <v>4068100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4212400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>3942700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4158700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3385300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3382900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3327700</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O49" s="3">
         <v>3382900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3327700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3053200</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2516,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2563,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F52" s="3">
         <v>12900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>12600</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>13100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>13000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>26000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>52200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>26000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>52200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2657,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9464200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9551500</v>
+      </c>
+      <c r="F54" s="3">
         <v>9523800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9425200</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
         <v>8782800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8937600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7378800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7247700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6428700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>7247700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6428700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5898500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2727,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2746,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>696900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>703300</v>
+      </c>
+      <c r="F57" s="3">
         <v>839000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>639300</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
         <v>696400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>572200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>576000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>599900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>578800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>599900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>578800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>531100</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>324000</v>
+      </c>
+      <c r="F58" s="3">
         <v>401400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>447600</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>354000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>324800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>540200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>441200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>148600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>441200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>148600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>136300</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>131400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>132600</v>
+      </c>
+      <c r="F59" s="3">
         <v>109100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>88800</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>35900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>102100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>51300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>78700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>99100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>78700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>99100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1364100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1376700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1569400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1404500</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
         <v>1285700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1233800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1350800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1323900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>989200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>1323900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>989200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>907600</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2884700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2911300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2766800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2958900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>2816300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3035300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2228700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2276200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2050400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>2276200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2050400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1881300</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>65700</v>
+      </c>
+      <c r="F62" s="3">
         <v>80300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>112600</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
         <v>127800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>48600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>53600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>44700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>49700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>44700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>49700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>45600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3071,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3118,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3165,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4902300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4947500</v>
+      </c>
+      <c r="F66" s="3">
         <v>4986600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5068900</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
         <v>4791400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4865700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4143700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4141600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3567100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>4141600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3567100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3272900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3235,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3278,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3325,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3372,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3419,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3842100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3877600</v>
+      </c>
+      <c r="F72" s="3">
         <v>3947500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3765800</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>3203100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3963400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3174800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2987700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2754500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>2987700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2754500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2527400</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3513,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3560,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3607,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4560700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4602800</v>
+      </c>
+      <c r="F76" s="3">
         <v>4535400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4355000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4165600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3990100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4071600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3233300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3104600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2860100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>3104600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2860100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2624200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3701,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3800,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,13 +3823,15 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>34600</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>4</v>
@@ -3441,35 +3839,41 @@
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>17700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>16200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>17500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>18600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>16000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>16200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>17500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>16000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3913,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3960,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4007,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4054,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,25 +4101,31 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
+      <c r="D89" s="3">
+        <v>20600</v>
       </c>
       <c r="E89" s="3">
-        <v>97900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>90100</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
+        <v>20800</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3">
+        <v>98100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>90300</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>4</v>
@@ -3699,23 +4133,29 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>153200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>153200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>140600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4171,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>-47400</v>
       </c>
       <c r="E91" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
         <v>-58100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-53500</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-78800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-78800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-72300</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4261,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,25 +4308,31 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>15400</v>
       </c>
       <c r="E94" s="3">
-        <v>-54300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+        <v>15600</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-49700</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
@@ -3880,23 +4340,29 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-333400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-333400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-305900</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4378,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>68500</v>
       </c>
       <c r="E96" s="3">
+        <v>69200</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>45800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>42200</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4468,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4515,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,25 +4562,31 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>-42800</v>
       </c>
       <c r="E100" s="3">
-        <v>-145500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-133900</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
+        <v>-43200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-145600</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-134000</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
@@ -4102,28 +4594,34 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>145600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>145600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>-9200</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>4</v>
@@ -4131,53 +4629,59 @@
       <c r="F101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3">
         <v>-17600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-16100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>33700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>35800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>8200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-16100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>33700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>8200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-2900</v>
       </c>
       <c r="E102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-111600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-102700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -4185,18 +4689,24 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-52200</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-52200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-47900</v>
       </c>
     </row>
